--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08ABB30-1DD5-C84C-AD17-7F8C5D8A1E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D850BA-7EA8-4BD8-8DFC-ED06E3CE84FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38780" yWindow="380" windowWidth="28800" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -101,6 +117,15 @@
   </si>
   <si>
     <t>DLS2_Males</t>
+  </si>
+  <si>
+    <t>PW1d</t>
+  </si>
+  <si>
+    <t>PW1f</t>
+  </si>
+  <si>
+    <t>PW2c</t>
   </si>
 </sst>
 </file>
@@ -475,10 +500,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -494,7 +519,7 @@
         <v>0.81857066434101511</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -502,7 +527,7 @@
         <v>0.83183050833110173</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -510,7 +535,7 @@
         <v>0.52838226151512502</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -518,7 +543,7 @@
         <v>0.63794775886311106</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -526,7 +551,7 @@
         <v>1.7487317224564645</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -534,7 +559,7 @@
         <v>3.7549875108949018</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -542,7 +567,7 @@
         <v>6.4764075049781749</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -550,7 +575,7 @@
         <v>1.0366118799278699</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -558,7 +583,7 @@
         <v>0.85170355381228569</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -566,7 +591,7 @@
         <v>1.1480377870969753</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -574,7 +599,7 @@
         <v>1.1960390964496237</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -582,7 +607,7 @@
         <v>4.460523583140219</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -590,7 +615,7 @@
         <v>4.2529536919897684</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -598,7 +623,7 @@
         <v>3.7382957371324035</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -606,7 +631,7 @@
         <v>2.5977267935063337</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -614,7 +639,7 @@
         <v>2.1895888225015536</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -622,7 +647,7 @@
         <v>7.9661177286442255</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -630,7 +655,7 @@
         <v>7.1714148232921389</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -638,7 +663,7 @@
         <v>6.4840573935244814</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -646,7 +671,7 @@
         <v>7.0657713186475233</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -654,7 +679,7 @@
         <v>6.0610553268076588</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -662,7 +687,7 @@
         <v>5.4194767626250133</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -670,7 +695,7 @@
         <v>1.9023687544636687</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -678,12 +703,36 @@
         <v>1.7145370168869383</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
         <v>1.6259752837992298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>0.98090109999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>0.77345540000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>1.0740229999999999</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dasha\ESSEX\_SimPaths\_SimPaths_UK\input_processing\regression_estimates\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD2E4EB-0516-4B27-A05C-B535DEC893B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B4A97A-11EB-43BF-9DFE-4390FC3D442C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="1750" windowWidth="28800" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -101,6 +106,18 @@
   </si>
   <si>
     <t>DLS2_Males</t>
+  </si>
+  <si>
+    <t>PW1d</t>
+  </si>
+  <si>
+    <t>PW1f</t>
+  </si>
+  <si>
+    <t>PW2c</t>
+  </si>
+  <si>
+    <t>FW1a</t>
   </si>
 </sst>
 </file>
@@ -469,13 +486,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38.140625" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,7 +500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -491,7 +508,7 @@
         <v>0.81845421244698169</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -499,7 +516,7 @@
         <v>0.8318231278642283</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -507,7 +524,7 @@
         <v>0.52842580917125537</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -515,7 +532,7 @@
         <v>0.63796656252519179</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -523,7 +540,7 @@
         <v>1.7455110656071953</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -531,7 +548,7 @@
         <v>0.97409509625211432</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -539,7 +556,7 @@
         <v>1.1365855588198837</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -547,7 +564,7 @@
         <v>1.036047441983782</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -555,7 +572,7 @@
         <v>0.84870070750541715</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -563,7 +580,7 @@
         <v>1.1484500852818154</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -571,7 +588,7 @@
         <v>1.1927903832324709</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -579,7 +596,7 @@
         <v>4.4608727317206842</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -587,7 +604,7 @@
         <v>4.2488100047405588</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -595,7 +612,7 @@
         <v>3.7376343170238648</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -603,7 +620,7 @@
         <v>2.5968664130199306</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -611,7 +628,7 @@
         <v>2.1885543164797094</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -619,7 +636,7 @@
         <v>7.966919324090096</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -627,7 +644,7 @@
         <v>7.1657841258237269</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -635,7 +652,7 @@
         <v>6.4859586641425091</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -643,7 +660,7 @@
         <v>7.0661394726712041</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -651,7 +668,7 @@
         <v>6.0523880929117633</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -659,7 +676,7 @@
         <v>5.4222029042219946</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -667,7 +684,7 @@
         <v>1.902513219539105</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -675,12 +692,44 @@
         <v>1.7134881680118068</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
         <v>1.6261256004830791</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27">
+        <v>0.98090109999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>0.77345540000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>1.0740229999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>0.50560000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B4A97A-11EB-43BF-9DFE-4390FC3D442C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F39765-0403-4026-9E5B-556F09754A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="1750" windowWidth="28800" windowHeight="15290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -118,6 +129,12 @@
   </si>
   <si>
     <t>FW1a</t>
+  </si>
+  <si>
+    <t>HW1c</t>
+  </si>
+  <si>
+    <t>HW1d</t>
   </si>
 </sst>
 </file>
@@ -486,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.1796875" customWidth="1"/>
@@ -732,6 +749,22 @@
         <v>0.50560000000000005</v>
       </c>
     </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>0.95802536417754225</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>2.3250999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -1,42 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hrushikeshkalakandra/Documents/GitHub/wealth/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F39765-0403-4026-9E5B-556F09754A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{255E6772-B98C-B74C-A2DC-968FAD52318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="640" windowWidth="30160" windowHeight="19000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -56,6 +40,15 @@
     <t>W1mb</t>
   </si>
   <si>
+    <t>I1b</t>
+  </si>
+  <si>
+    <t>I2b</t>
+  </si>
+  <si>
+    <t>I3b</t>
+  </si>
+  <si>
     <t>S2d</t>
   </si>
   <si>
@@ -68,15 +61,6 @@
     <t>S3d</t>
   </si>
   <si>
-    <t>I1b</t>
-  </si>
-  <si>
-    <t>I2b</t>
-  </si>
-  <si>
-    <t>I3b</t>
-  </si>
-  <si>
     <t>HM1_L</t>
   </si>
   <si>
@@ -135,6 +119,12 @@
   </si>
   <si>
     <t>HW1d</t>
+  </si>
+  <si>
+    <t>HW2c</t>
+  </si>
+  <si>
+    <t>HW2d</t>
   </si>
 </sst>
 </file>
@@ -187,7 +177,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -229,108 +219,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -338,80 +234,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -441,22 +288,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -471,45 +318,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.1796875" customWidth="1"/>
+    <col min="1" max="1" width="38.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -525,7 +347,7 @@
         <v>0.81845421244698169</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -533,7 +355,7 @@
         <v>0.8318231278642283</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -541,7 +363,7 @@
         <v>0.52842580917125537</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -549,63 +371,63 @@
         <v>0.63796656252519179</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1.7455110656071953</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.745511065607195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>0.97409509625211432</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>1.1365855588198837</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.1365855588198841</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>1.036047441983782</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>0.84870070750541715</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B11">
-        <v>1.1484500852818154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.1484500852818149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12">
-        <v>1.1927903832324709</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.1927903832324711</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -613,7 +435,7 @@
         <v>4.4608727317206842</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -621,7 +443,7 @@
         <v>4.2488100047405588</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -629,23 +451,23 @@
         <v>3.7376343170238648</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.5968664130199306</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.596866413019931</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
-        <v>2.1885543164797094</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2.188554316479709</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -653,7 +475,7 @@
         <v>7.966919324090096</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -661,7 +483,7 @@
         <v>7.1657841258237269</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -669,7 +491,7 @@
         <v>6.4859586641425091</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -677,7 +499,7 @@
         <v>7.0661394726712041</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -685,7 +507,7 @@
         <v>6.0523880929117633</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -693,7 +515,7 @@
         <v>5.4222029042219946</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -701,15 +523,15 @@
         <v>1.902513219539105</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1.7134881680118068</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>1.713488168011807</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -717,7 +539,7 @@
         <v>1.6261256004830791</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -725,7 +547,7 @@
         <v>0.98090109999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -733,7 +555,7 @@
         <v>0.77345540000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -741,7 +563,7 @@
         <v>1.0740229999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -749,7 +571,7 @@
         <v>0.50560000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -757,12 +579,28 @@
         <v>0.95802536417754225</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>32</v>
       </c>
       <c r="B32">
         <v>2.3250999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>0.41646133070000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>0.80487359000000003</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="1" r:id="R79d909dd203b4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="1" r:id="R52cca3e2589e4f37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,9 +85,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -479,7 +479,7 @@
         <x:v>FW2c</x:v>
       </x:c>
       <x:c r="B36" t="n">
-        <x:v>1.1064186435860763</x:v>
+        <x:v>1.13574141020715</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -495,7 +495,7 @@
         <x:v>FW2e</x:v>
       </x:c>
       <x:c r="B38" t="n">
-        <x:v>1.004758156254813</x:v>
+        <x:v>0.9720760974457268</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\99 DEV ENV\JAS-MINE\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7602986-33BD-45BB-8F36-953D409EBE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7296AE34-F10A-4EE7-85E3-28BED895BB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29160" yWindow="1280" windowWidth="28800" windowHeight="15430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UK" sheetId="1" r:id="rId1"/>
@@ -611,7 +611,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>2.3250999999999999</v>
+        <v>0.55981284625299998</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
